--- a/IT Actions Dimonekene.xlsx
+++ b/IT Actions Dimonekene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B.NIMI\Desktop\DIVERS\Fichiers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF40F312-2D76-4864-AE2D-E4077217B71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09720375-B8BB-4075-90D3-FB5FADF16A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" firstSheet="5" activeTab="6" xr2:uid="{E9D5118C-A769-4C44-AF96-8C3A56EDA7ED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="6" xr2:uid="{E9D5118C-A769-4C44-AF96-8C3A56EDA7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="IT Action 28-02-22" sheetId="1" state="hidden" r:id="rId1"/>
@@ -993,16 +993,16 @@
           </t>
   </si>
   <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>09/09/2026</t>
-  </si>
-  <si>
     <t>Déduction des heures de nuit</t>
   </si>
   <si>
     <t>Déduction des complement</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D5" s="8">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D6" s="8">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="10"/>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D7" s="8">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
@@ -9408,13 +9408,13 @@
         <v>104</v>
       </c>
       <c r="F2" s="67" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G2" s="67" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="67" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I2" s="64"/>
       <c r="J2" s="64"/>
@@ -9425,7 +9425,7 @@
         <v>119</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C3" s="64"/>
       <c r="D3" s="66"/>
@@ -9450,7 +9450,7 @@
         <v>123</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C4" s="64"/>
       <c r="D4" s="64"/>
